--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>1942</v>
+        <v>2608</v>
       </c>
       <c r="E2" t="n">
-        <v>149.38</v>
+        <v>200.62</v>
       </c>
     </row>
     <row r="3">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3354</v>
+        <v>974</v>
       </c>
       <c r="E3" t="n">
-        <v>139.75</v>
+        <v>194.8</v>
       </c>
     </row>
     <row r="4">
@@ -487,17 +487,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>821</v>
+        <v>4538</v>
       </c>
       <c r="E4" t="n">
-        <v>136.83</v>
+        <v>189.08</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>798</v>
+        <v>1094</v>
       </c>
       <c r="E5" t="n">
-        <v>133</v>
+        <v>182.33</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>3523</v>
+        <v>4929</v>
       </c>
       <c r="E6" t="n">
-        <v>113.65</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7">
@@ -551,10 +551,10 @@
         <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>1835</v>
+        <v>2649</v>
       </c>
       <c r="E7" t="n">
-        <v>107.94</v>
+        <v>155.82</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -449,17 +449,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>2608</v>
+        <v>1233</v>
       </c>
       <c r="E2" t="n">
-        <v>200.62</v>
+        <v>205.5</v>
       </c>
     </row>
     <row r="3">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>974</v>
+        <v>1353</v>
       </c>
       <c r="E3" t="n">
-        <v>194.8</v>
+        <v>193.29</v>
       </c>
     </row>
     <row r="4">
@@ -506,17 +506,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>1094</v>
+        <v>2751</v>
       </c>
       <c r="E5" t="n">
-        <v>182.33</v>
+        <v>183.4</v>
       </c>
     </row>
     <row r="6">
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>4929</v>
+        <v>5175</v>
       </c>
       <c r="E6" t="n">
-        <v>159</v>
+        <v>156.82</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>2649</v>
+        <v>2772</v>
       </c>
       <c r="E7" t="n">
-        <v>155.82</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,17 +449,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>1233</v>
+        <v>2999</v>
       </c>
       <c r="E2" t="n">
-        <v>205.5</v>
+        <v>230.69</v>
       </c>
     </row>
     <row r="3">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>1353</v>
+        <v>5380</v>
       </c>
       <c r="E3" t="n">
-        <v>193.29</v>
+        <v>224.17</v>
       </c>
     </row>
     <row r="4">
@@ -487,17 +487,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>4538</v>
+        <v>3213</v>
       </c>
       <c r="E4" t="n">
-        <v>189.08</v>
+        <v>214.2</v>
       </c>
     </row>
     <row r="5">
@@ -506,17 +506,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>2751</v>
+        <v>3417</v>
       </c>
       <c r="E5" t="n">
-        <v>183.4</v>
+        <v>189.83</v>
       </c>
     </row>
     <row r="6">
@@ -532,29 +532,10 @@
         <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>5175</v>
+        <v>6215</v>
       </c>
       <c r="E6" t="n">
-        <v>156.82</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>18</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2772</v>
-      </c>
-      <c r="E7" t="n">
-        <v>154</v>
+        <v>188.33</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>2999</v>
+        <v>2747</v>
       </c>
       <c r="E2" t="n">
-        <v>230.69</v>
+        <v>211.31</v>
       </c>
     </row>
     <row r="3">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>5380</v>
+        <v>2892</v>
       </c>
       <c r="E3" t="n">
-        <v>224.17</v>
+        <v>192.8</v>
       </c>
     </row>
     <row r="4">
@@ -487,17 +487,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>3213</v>
+        <v>4538</v>
       </c>
       <c r="E4" t="n">
-        <v>214.2</v>
+        <v>189.08</v>
       </c>
     </row>
     <row r="5">
@@ -506,17 +506,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>3417</v>
+        <v>5477</v>
       </c>
       <c r="E5" t="n">
-        <v>189.83</v>
+        <v>165.97</v>
       </c>
     </row>
     <row r="6">
@@ -525,17 +525,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>6215</v>
+        <v>2933</v>
       </c>
       <c r="E6" t="n">
-        <v>188.33</v>
+        <v>162.94</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>2747</v>
+        <v>3315</v>
       </c>
       <c r="E2" t="n">
-        <v>211.31</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>2892</v>
+        <v>5938</v>
       </c>
       <c r="E3" t="n">
-        <v>192.8</v>
+        <v>247.42</v>
       </c>
     </row>
     <row r="4">
@@ -487,17 +487,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>4538</v>
+        <v>3542</v>
       </c>
       <c r="E4" t="n">
-        <v>189.08</v>
+        <v>236.13</v>
       </c>
     </row>
     <row r="5">
@@ -506,17 +506,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>5477</v>
+        <v>3847</v>
       </c>
       <c r="E5" t="n">
-        <v>165.97</v>
+        <v>213.72</v>
       </c>
     </row>
     <row r="6">
@@ -525,17 +525,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>2933</v>
+        <v>6797</v>
       </c>
       <c r="E6" t="n">
-        <v>162.94</v>
+        <v>205.97</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>3315</v>
+        <v>4377</v>
       </c>
       <c r="E2" t="n">
-        <v>255</v>
+        <v>336.69</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>5938</v>
+        <v>7156</v>
       </c>
       <c r="E3" t="n">
-        <v>247.42</v>
+        <v>298.17</v>
       </c>
     </row>
     <row r="4">
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>3542</v>
+        <v>3971</v>
       </c>
       <c r="E4" t="n">
-        <v>236.13</v>
+        <v>283.64</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>3847</v>
+        <v>4903</v>
       </c>
       <c r="E5" t="n">
-        <v>213.72</v>
+        <v>272.39</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>6797</v>
+        <v>8243</v>
       </c>
       <c r="E6" t="n">
-        <v>205.97</v>
+        <v>249.79</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>4377</v>
+        <v>4557</v>
       </c>
       <c r="E2" t="n">
-        <v>336.69</v>
+        <v>350.54</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>7156</v>
+        <v>7486</v>
       </c>
       <c r="E3" t="n">
-        <v>298.17</v>
+        <v>311.92</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>3971</v>
+        <v>4181</v>
       </c>
       <c r="E4" t="n">
-        <v>283.64</v>
+        <v>298.64</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>4903</v>
+        <v>5143</v>
       </c>
       <c r="E5" t="n">
-        <v>272.39</v>
+        <v>285.72</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>8243</v>
+        <v>8708</v>
       </c>
       <c r="E6" t="n">
-        <v>249.79</v>
+        <v>263.88</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -449,17 +449,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>4557</v>
+        <v>6627</v>
       </c>
       <c r="E2" t="n">
-        <v>350.54</v>
+        <v>473.36</v>
       </c>
     </row>
     <row r="3">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>7486</v>
+        <v>6069</v>
       </c>
       <c r="E3" t="n">
-        <v>311.92</v>
+        <v>466.85</v>
       </c>
     </row>
     <row r="4">
@@ -487,17 +487,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>4181</v>
+        <v>10804</v>
       </c>
       <c r="E4" t="n">
-        <v>298.64</v>
+        <v>450.17</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>5143</v>
+        <v>7574</v>
       </c>
       <c r="E5" t="n">
-        <v>285.72</v>
+        <v>420.78</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>8708</v>
+        <v>12326</v>
       </c>
       <c r="E6" t="n">
-        <v>263.88</v>
+        <v>373.52</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>6627</v>
+        <v>6897</v>
       </c>
       <c r="E2" t="n">
-        <v>473.36</v>
+        <v>492.64</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>6069</v>
+        <v>6204</v>
       </c>
       <c r="E3" t="n">
-        <v>466.85</v>
+        <v>477.23</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>10804</v>
+        <v>10970</v>
       </c>
       <c r="E4" t="n">
-        <v>450.17</v>
+        <v>457.08</v>
       </c>
     </row>
     <row r="5">
@@ -532,10 +532,10 @@
         <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>12326</v>
+        <v>13094</v>
       </c>
       <c r="E6" t="n">
-        <v>373.52</v>
+        <v>396.79</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -449,17 +449,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>6897</v>
+        <v>7610</v>
       </c>
       <c r="E2" t="n">
-        <v>492.64</v>
+        <v>585.38</v>
       </c>
     </row>
     <row r="3">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>6204</v>
+        <v>7994</v>
       </c>
       <c r="E3" t="n">
-        <v>477.23</v>
+        <v>571</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>10970</v>
+        <v>12452</v>
       </c>
       <c r="E4" t="n">
-        <v>457.08</v>
+        <v>518.83</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>7574</v>
+        <v>9184</v>
       </c>
       <c r="E5" t="n">
-        <v>420.78</v>
+        <v>510.22</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>13094</v>
+        <v>16283</v>
       </c>
       <c r="E6" t="n">
-        <v>396.79</v>
+        <v>493.42</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>7610</v>
+        <v>8130</v>
       </c>
       <c r="E2" t="n">
-        <v>585.38</v>
+        <v>625.38</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>7994</v>
+        <v>8514</v>
       </c>
       <c r="E3" t="n">
-        <v>571</v>
+        <v>608.14</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>12452</v>
+        <v>13506</v>
       </c>
       <c r="E4" t="n">
-        <v>518.83</v>
+        <v>562.75</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>9184</v>
+        <v>10056</v>
       </c>
       <c r="E5" t="n">
-        <v>510.22</v>
+        <v>558.67</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>16283</v>
+        <v>17915</v>
       </c>
       <c r="E6" t="n">
-        <v>493.42</v>
+        <v>542.88</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>8130</v>
+        <v>11274</v>
       </c>
       <c r="E2" t="n">
-        <v>625.38</v>
+        <v>867.23</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>8514</v>
+        <v>11984</v>
       </c>
       <c r="E3" t="n">
-        <v>608.14</v>
+        <v>856</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>13506</v>
+        <v>20404</v>
       </c>
       <c r="E4" t="n">
-        <v>562.75</v>
+        <v>850.17</v>
       </c>
     </row>
     <row r="5">
@@ -506,17 +506,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>10056</v>
+        <v>26702</v>
       </c>
       <c r="E5" t="n">
-        <v>558.67</v>
+        <v>809.15</v>
       </c>
     </row>
     <row r="6">
@@ -525,17 +525,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>17915</v>
+        <v>13994</v>
       </c>
       <c r="E6" t="n">
-        <v>542.88</v>
+        <v>777.4400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>11274</v>
+        <v>13038</v>
       </c>
       <c r="E2" t="n">
-        <v>867.23</v>
+        <v>1002.92</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>11984</v>
+        <v>12772</v>
       </c>
       <c r="E3" t="n">
-        <v>856</v>
+        <v>912.29</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>20404</v>
+        <v>21474</v>
       </c>
       <c r="E4" t="n">
-        <v>850.17</v>
+        <v>894.75</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>26702</v>
+        <v>29283</v>
       </c>
       <c r="E5" t="n">
-        <v>809.15</v>
+        <v>887.36</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>13994</v>
+        <v>15523</v>
       </c>
       <c r="E6" t="n">
-        <v>777.4400000000001</v>
+        <v>862.39</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>13038</v>
+        <v>15491</v>
       </c>
       <c r="E2" t="n">
-        <v>1002.92</v>
+        <v>1191.62</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>12772</v>
+        <v>15942</v>
       </c>
       <c r="E3" t="n">
-        <v>912.29</v>
+        <v>1138.71</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>21474</v>
+        <v>26804</v>
       </c>
       <c r="E4" t="n">
-        <v>894.75</v>
+        <v>1116.83</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>29283</v>
+        <v>36416</v>
       </c>
       <c r="E5" t="n">
-        <v>887.36</v>
+        <v>1103.52</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>15523</v>
+        <v>18993</v>
       </c>
       <c r="E6" t="n">
-        <v>862.39</v>
+        <v>1055.17</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>15491</v>
+        <v>17630</v>
       </c>
       <c r="E2" t="n">
-        <v>1191.62</v>
+        <v>1356.15</v>
       </c>
     </row>
     <row r="3">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>15942</v>
+        <v>42081</v>
       </c>
       <c r="E3" t="n">
-        <v>1138.71</v>
+        <v>1275.18</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>26804</v>
+        <v>30487</v>
       </c>
       <c r="E4" t="n">
-        <v>1116.83</v>
+        <v>1270.29</v>
       </c>
     </row>
     <row r="5">
@@ -506,17 +506,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>36416</v>
+        <v>17477</v>
       </c>
       <c r="E5" t="n">
-        <v>1103.52</v>
+        <v>1248.36</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>18993</v>
+        <v>21836</v>
       </c>
       <c r="E6" t="n">
-        <v>1055.17</v>
+        <v>1213.11</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>17630</v>
+        <v>19019</v>
       </c>
       <c r="E2" t="n">
-        <v>1356.15</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="3">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>42081</v>
+        <v>19978</v>
       </c>
       <c r="E3" t="n">
-        <v>1275.18</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="4">
@@ -487,17 +487,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>30487</v>
+        <v>46713</v>
       </c>
       <c r="E4" t="n">
-        <v>1270.29</v>
+        <v>1415.55</v>
       </c>
     </row>
     <row r="5">
@@ -506,17 +506,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>17477</v>
+        <v>33262</v>
       </c>
       <c r="E5" t="n">
-        <v>1248.36</v>
+        <v>1385.92</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>21836</v>
+        <v>24077</v>
       </c>
       <c r="E6" t="n">
-        <v>1213.11</v>
+        <v>1337.61</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>19019</v>
+        <v>21137</v>
       </c>
       <c r="E2" t="n">
-        <v>1463</v>
+        <v>1625.92</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>19978</v>
+        <v>22396</v>
       </c>
       <c r="E3" t="n">
-        <v>1427</v>
+        <v>1599.71</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>46713</v>
+        <v>52595</v>
       </c>
       <c r="E4" t="n">
-        <v>1415.55</v>
+        <v>1593.79</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>33262</v>
+        <v>37349</v>
       </c>
       <c r="E5" t="n">
-        <v>1385.92</v>
+        <v>1556.21</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>24077</v>
+        <v>26847</v>
       </c>
       <c r="E6" t="n">
-        <v>1337.61</v>
+        <v>1491.5</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>21137</v>
+        <v>22468</v>
       </c>
       <c r="E2" t="n">
-        <v>1625.92</v>
+        <v>1728.31</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>22396</v>
+        <v>23982</v>
       </c>
       <c r="E3" t="n">
-        <v>1599.71</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>52595</v>
+        <v>56301</v>
       </c>
       <c r="E4" t="n">
-        <v>1593.79</v>
+        <v>1706.09</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>37349</v>
+        <v>39668</v>
       </c>
       <c r="E5" t="n">
-        <v>1556.21</v>
+        <v>1652.83</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>26847</v>
+        <v>28978</v>
       </c>
       <c r="E6" t="n">
-        <v>1491.5</v>
+        <v>1609.89</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -449,17 +449,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>22468</v>
+        <v>27287</v>
       </c>
       <c r="E2" t="n">
-        <v>1728.31</v>
+        <v>1949.07</v>
       </c>
     </row>
     <row r="3">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>23982</v>
+        <v>63819</v>
       </c>
       <c r="E3" t="n">
-        <v>1713</v>
+        <v>1933.91</v>
       </c>
     </row>
     <row r="4">
@@ -487,17 +487,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>56301</v>
+        <v>24960</v>
       </c>
       <c r="E4" t="n">
-        <v>1706.09</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>39668</v>
+        <v>44988</v>
       </c>
       <c r="E5" t="n">
-        <v>1652.83</v>
+        <v>1874.5</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>28978</v>
+        <v>32587</v>
       </c>
       <c r="E6" t="n">
-        <v>1609.89</v>
+        <v>1810.39</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,10 +456,10 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>27287</v>
+        <v>31285</v>
       </c>
       <c r="E2" t="n">
-        <v>1949.07</v>
+        <v>2234.64</v>
       </c>
     </row>
     <row r="3">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>63819</v>
+        <v>28486</v>
       </c>
       <c r="E3" t="n">
-        <v>1933.91</v>
+        <v>2191.23</v>
       </c>
     </row>
     <row r="4">
@@ -487,17 +487,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>24960</v>
+        <v>71123</v>
       </c>
       <c r="E4" t="n">
-        <v>1920</v>
+        <v>2155.24</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>44988</v>
+        <v>49896</v>
       </c>
       <c r="E5" t="n">
-        <v>1874.5</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>32587</v>
+        <v>36109</v>
       </c>
       <c r="E6" t="n">
-        <v>1810.39</v>
+        <v>2006.06</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>31285</v>
+        <v>35047</v>
       </c>
       <c r="E2" t="n">
-        <v>2234.64</v>
+        <v>2503.36</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>28486</v>
+        <v>32138</v>
       </c>
       <c r="E3" t="n">
-        <v>2191.23</v>
+        <v>2472.15</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>71123</v>
+        <v>80114</v>
       </c>
       <c r="E4" t="n">
-        <v>2155.24</v>
+        <v>2427.7</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>49896</v>
+        <v>57278</v>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>2386.58</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>36109</v>
+        <v>40357</v>
       </c>
       <c r="E6" t="n">
-        <v>2006.06</v>
+        <v>2242.06</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -453,13 +453,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>35047</v>
+        <v>41686</v>
       </c>
       <c r="E2" t="n">
-        <v>2503.36</v>
+        <v>2779.07</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>32138</v>
+        <v>35004</v>
       </c>
       <c r="E3" t="n">
-        <v>2472.15</v>
+        <v>2692.62</v>
       </c>
     </row>
     <row r="4">
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>80114</v>
+        <v>84932</v>
       </c>
       <c r="E4" t="n">
-        <v>2427.7</v>
+        <v>2654.12</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>57278</v>
+        <v>63554</v>
       </c>
       <c r="E5" t="n">
-        <v>2386.58</v>
+        <v>2648.08</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>40357</v>
+        <v>44104</v>
       </c>
       <c r="E6" t="n">
-        <v>2242.06</v>
+        <v>2450.22</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>41686</v>
+        <v>42604</v>
       </c>
       <c r="E2" t="n">
-        <v>2779.07</v>
+        <v>2840.27</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>35004</v>
+        <v>35780</v>
       </c>
       <c r="E3" t="n">
-        <v>2692.62</v>
+        <v>2752.31</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>84932</v>
+        <v>86974</v>
       </c>
       <c r="E4" t="n">
-        <v>2654.12</v>
+        <v>2717.94</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>63554</v>
+        <v>64892</v>
       </c>
       <c r="E5" t="n">
-        <v>2648.08</v>
+        <v>2703.83</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>44104</v>
+        <v>44794</v>
       </c>
       <c r="E6" t="n">
-        <v>2450.22</v>
+        <v>2488.56</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>42604</v>
+        <v>44180</v>
       </c>
       <c r="E2" t="n">
-        <v>2840.27</v>
+        <v>2945.33</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>35780</v>
+        <v>36952</v>
       </c>
       <c r="E3" t="n">
-        <v>2752.31</v>
+        <v>2842.46</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>86974</v>
+        <v>90089</v>
       </c>
       <c r="E4" t="n">
-        <v>2717.94</v>
+        <v>2815.28</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>64892</v>
+        <v>66907</v>
       </c>
       <c r="E5" t="n">
-        <v>2703.83</v>
+        <v>2787.79</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>44794</v>
+        <v>46129</v>
       </c>
       <c r="E6" t="n">
-        <v>2488.56</v>
+        <v>2562.72</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>44180</v>
+        <v>46259</v>
       </c>
       <c r="E2" t="n">
-        <v>2945.33</v>
+        <v>3083.93</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>36952</v>
+        <v>38872</v>
       </c>
       <c r="E3" t="n">
-        <v>2842.46</v>
+        <v>2990.15</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>90089</v>
+        <v>94722</v>
       </c>
       <c r="E4" t="n">
-        <v>2815.28</v>
+        <v>2960.06</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>66907</v>
+        <v>70418</v>
       </c>
       <c r="E5" t="n">
-        <v>2787.79</v>
+        <v>2934.08</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>46129</v>
+        <v>49011</v>
       </c>
       <c r="E6" t="n">
-        <v>2562.72</v>
+        <v>2722.83</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>46259</v>
+        <v>46827</v>
       </c>
       <c r="E2" t="n">
-        <v>3083.93</v>
+        <v>3121.8</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>38872</v>
+        <v>39451</v>
       </c>
       <c r="E3" t="n">
-        <v>2990.15</v>
+        <v>3034.69</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>94722</v>
+        <v>96153</v>
       </c>
       <c r="E4" t="n">
-        <v>2960.06</v>
+        <v>3004.78</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>70418</v>
+        <v>71270</v>
       </c>
       <c r="E5" t="n">
-        <v>2934.08</v>
+        <v>2969.58</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>49011</v>
+        <v>49735</v>
       </c>
       <c r="E6" t="n">
-        <v>2722.83</v>
+        <v>2763.06</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>46827</v>
+        <v>48207</v>
       </c>
       <c r="E2" t="n">
-        <v>3121.8</v>
+        <v>3213.8</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>39451</v>
+        <v>40647</v>
       </c>
       <c r="E3" t="n">
-        <v>3034.69</v>
+        <v>3126.69</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>96153</v>
+        <v>98417</v>
       </c>
       <c r="E4" t="n">
-        <v>3004.78</v>
+        <v>3075.53</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>71270</v>
+        <v>72790</v>
       </c>
       <c r="E5" t="n">
-        <v>2969.58</v>
+        <v>3032.92</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>49735</v>
+        <v>51159</v>
       </c>
       <c r="E6" t="n">
-        <v>2763.06</v>
+        <v>2842.17</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>48207</v>
+        <v>50530</v>
       </c>
       <c r="E2" t="n">
-        <v>3213.8</v>
+        <v>3368.67</v>
       </c>
     </row>
     <row r="3">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>40647</v>
+        <v>46600</v>
       </c>
       <c r="E3" t="n">
-        <v>3126.69</v>
+        <v>3328.57</v>
       </c>
     </row>
     <row r="4">
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>98417</v>
+        <v>98902</v>
       </c>
       <c r="E4" t="n">
-        <v>3075.53</v>
+        <v>3190.39</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>72790</v>
+        <v>75963</v>
       </c>
       <c r="E5" t="n">
-        <v>3032.92</v>
+        <v>3165.12</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>51159</v>
+        <v>53419</v>
       </c>
       <c r="E6" t="n">
-        <v>2842.17</v>
+        <v>2967.72</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>50530</v>
+        <v>51939</v>
       </c>
       <c r="E2" t="n">
-        <v>3368.67</v>
+        <v>3462.6</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>46600</v>
+        <v>48089</v>
       </c>
       <c r="E3" t="n">
-        <v>3328.57</v>
+        <v>3434.93</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>98902</v>
+        <v>102062</v>
       </c>
       <c r="E4" t="n">
-        <v>3190.39</v>
+        <v>3292.32</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>75963</v>
+        <v>78606</v>
       </c>
       <c r="E5" t="n">
-        <v>3165.12</v>
+        <v>3275.25</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>53419</v>
+        <v>55014</v>
       </c>
       <c r="E6" t="n">
-        <v>2967.72</v>
+        <v>3056.33</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>51939</v>
+        <v>53393</v>
       </c>
       <c r="E2" t="n">
-        <v>3462.6</v>
+        <v>3559.53</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>48089</v>
+        <v>49421</v>
       </c>
       <c r="E3" t="n">
-        <v>3434.93</v>
+        <v>3530.07</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>102062</v>
+        <v>104754</v>
       </c>
       <c r="E4" t="n">
-        <v>3292.32</v>
+        <v>3379.16</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>78606</v>
+        <v>80542</v>
       </c>
       <c r="E5" t="n">
-        <v>3275.25</v>
+        <v>3355.92</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>55014</v>
+        <v>56454</v>
       </c>
       <c r="E6" t="n">
-        <v>3056.33</v>
+        <v>3136.33</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>53393</v>
+        <v>54195</v>
       </c>
       <c r="E2" t="n">
-        <v>3559.53</v>
+        <v>3613</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>49421</v>
+        <v>49979</v>
       </c>
       <c r="E3" t="n">
-        <v>3530.07</v>
+        <v>3569.93</v>
       </c>
     </row>
     <row r="4">
@@ -487,17 +487,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>104754</v>
+        <v>82292</v>
       </c>
       <c r="E4" t="n">
-        <v>3379.16</v>
+        <v>3428.83</v>
       </c>
     </row>
     <row r="5">
@@ -506,17 +506,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>80542</v>
+        <v>106165</v>
       </c>
       <c r="E5" t="n">
-        <v>3355.92</v>
+        <v>3424.68</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>56454</v>
+        <v>57235</v>
       </c>
       <c r="E6" t="n">
-        <v>3136.33</v>
+        <v>3179.72</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>54195</v>
+        <v>55121</v>
       </c>
       <c r="E2" t="n">
-        <v>3613</v>
+        <v>3674.73</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>49979</v>
+        <v>50789</v>
       </c>
       <c r="E3" t="n">
-        <v>3569.93</v>
+        <v>3627.79</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>82292</v>
+        <v>83856</v>
       </c>
       <c r="E4" t="n">
-        <v>3428.83</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>106165</v>
+        <v>107973</v>
       </c>
       <c r="E5" t="n">
-        <v>3424.68</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>57235</v>
+        <v>58539</v>
       </c>
       <c r="E6" t="n">
-        <v>3179.72</v>
+        <v>3252.17</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>55121</v>
+        <v>55836</v>
       </c>
       <c r="E2" t="n">
-        <v>3674.73</v>
+        <v>3722.4</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>50789</v>
+        <v>51558</v>
       </c>
       <c r="E3" t="n">
-        <v>3627.79</v>
+        <v>3682.71</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>83856</v>
+        <v>85055</v>
       </c>
       <c r="E4" t="n">
-        <v>3494</v>
+        <v>3543.96</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>107973</v>
+        <v>109683</v>
       </c>
       <c r="E5" t="n">
-        <v>3483</v>
+        <v>3538.16</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>58539</v>
+        <v>59507</v>
       </c>
       <c r="E6" t="n">
-        <v>3252.17</v>
+        <v>3305.94</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>55836</v>
+        <v>56742</v>
       </c>
       <c r="E2" t="n">
-        <v>3722.4</v>
+        <v>3782.8</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>51558</v>
+        <v>52302</v>
       </c>
       <c r="E3" t="n">
-        <v>3682.71</v>
+        <v>3735.86</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>85055</v>
+        <v>86439</v>
       </c>
       <c r="E4" t="n">
-        <v>3543.96</v>
+        <v>3601.62</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>109683</v>
+        <v>111229</v>
       </c>
       <c r="E5" t="n">
-        <v>3538.16</v>
+        <v>3588.03</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>59507</v>
+        <v>60421</v>
       </c>
       <c r="E6" t="n">
-        <v>3305.94</v>
+        <v>3356.72</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>56742</v>
+        <v>57362</v>
       </c>
       <c r="E2" t="n">
-        <v>3782.8</v>
+        <v>3824.13</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>52302</v>
+        <v>52922</v>
       </c>
       <c r="E3" t="n">
-        <v>3735.86</v>
+        <v>3780.14</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>86439</v>
+        <v>87459</v>
       </c>
       <c r="E4" t="n">
-        <v>3601.62</v>
+        <v>3644.12</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>111229</v>
+        <v>112429</v>
       </c>
       <c r="E5" t="n">
-        <v>3588.03</v>
+        <v>3626.74</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>60421</v>
+        <v>61221</v>
       </c>
       <c r="E6" t="n">
-        <v>3356.72</v>
+        <v>3401.17</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>57362</v>
+        <v>59013</v>
       </c>
       <c r="E2" t="n">
-        <v>3824.13</v>
+        <v>3934.2</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>52922</v>
+        <v>54476</v>
       </c>
       <c r="E3" t="n">
-        <v>3780.14</v>
+        <v>3891.14</v>
       </c>
     </row>
     <row r="4">
@@ -487,17 +487,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>87459</v>
+        <v>115169</v>
       </c>
       <c r="E4" t="n">
-        <v>3644.12</v>
+        <v>3715.13</v>
       </c>
     </row>
     <row r="5">
@@ -506,17 +506,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>112429</v>
+        <v>88947</v>
       </c>
       <c r="E5" t="n">
-        <v>3626.74</v>
+        <v>3706.12</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>61221</v>
+        <v>62794</v>
       </c>
       <c r="E6" t="n">
-        <v>3401.17</v>
+        <v>3488.56</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>59013</v>
+        <v>59128</v>
       </c>
       <c r="E2" t="n">
-        <v>3934.2</v>
+        <v>3941.87</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>54476</v>
+        <v>54591</v>
       </c>
       <c r="E3" t="n">
-        <v>3891.14</v>
+        <v>3899.36</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>115169</v>
+        <v>115514</v>
       </c>
       <c r="E4" t="n">
-        <v>3715.13</v>
+        <v>3726.26</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>88947</v>
+        <v>89177</v>
       </c>
       <c r="E5" t="n">
-        <v>3706.12</v>
+        <v>3715.71</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>62794</v>
+        <v>62909</v>
       </c>
       <c r="E6" t="n">
-        <v>3488.56</v>
+        <v>3494.94</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>59128</v>
+        <v>59902</v>
       </c>
       <c r="E2" t="n">
-        <v>3941.87</v>
+        <v>3993.47</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>54591</v>
+        <v>54829</v>
       </c>
       <c r="E3" t="n">
-        <v>3899.36</v>
+        <v>3916.36</v>
       </c>
     </row>
     <row r="4">
@@ -487,17 +487,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>115514</v>
+        <v>89911</v>
       </c>
       <c r="E4" t="n">
-        <v>3726.26</v>
+        <v>3746.29</v>
       </c>
     </row>
     <row r="5">
@@ -506,17 +506,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>89177</v>
+        <v>115623</v>
       </c>
       <c r="E5" t="n">
-        <v>3715.71</v>
+        <v>3729.77</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>62909</v>
+        <v>63623</v>
       </c>
       <c r="E6" t="n">
-        <v>3494.94</v>
+        <v>3534.61</v>
       </c>
     </row>
   </sheetData>

--- a/classement_services.xlsx
+++ b/classement_services.xlsx
@@ -456,10 +456,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>59902</v>
+        <v>60820</v>
       </c>
       <c r="E2" t="n">
-        <v>3993.47</v>
+        <v>4054.67</v>
       </c>
     </row>
     <row r="3">
@@ -475,10 +475,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>54829</v>
+        <v>55988</v>
       </c>
       <c r="E3" t="n">
-        <v>3916.36</v>
+        <v>3999.14</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>89911</v>
+        <v>92070</v>
       </c>
       <c r="E4" t="n">
-        <v>3746.29</v>
+        <v>3836.25</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>115623</v>
+        <v>118452</v>
       </c>
       <c r="E5" t="n">
-        <v>3729.77</v>
+        <v>3821.03</v>
       </c>
     </row>
     <row r="6">
@@ -532,10 +532,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>63623</v>
+        <v>64922</v>
       </c>
       <c r="E6" t="n">
-        <v>3534.61</v>
+        <v>3606.78</v>
       </c>
     </row>
   </sheetData>
